--- a/DEV/org.openl.rules/test/rules/helpers/RulesUtilsTest.xlsx
+++ b/DEV/org.openl.rules/test/rules/helpers/RulesUtilsTest.xlsx
@@ -2621,33 +2621,21 @@
       <c r="B8" s="5" t="s">
         <v>268</v>
       </c>
-      <c r="D8" s="5" t="s">
-        <v>269</v>
-      </c>
     </row>
     <row r="9" spans="2:4" x14ac:dyDescent="0.2">
       <c r="B9" s="6" t="s">
         <v>264</v>
       </c>
-      <c r="D9" s="6" t="s">
-        <v>270</v>
-      </c>
     </row>
     <row r="11" spans="2:4" x14ac:dyDescent="0.2">
       <c r="B11" s="5" t="s">
         <v>271</v>
       </c>
-      <c r="D11" s="5" t="s">
-        <v>272</v>
-      </c>
     </row>
     <row r="12" spans="2:4" x14ac:dyDescent="0.2">
       <c r="B12" s="6" t="s">
         <v>267</v>
       </c>
-      <c r="D12" s="6" t="s">
-        <v>273</v>
-      </c>
     </row>
     <row r="14" spans="2:4" x14ac:dyDescent="0.2">
       <c r="B14" s="5" t="s">
@@ -2842,33 +2830,21 @@
       </c>
     </row>
     <row r="50" spans="2:4" x14ac:dyDescent="0.2">
-      <c r="B50" s="5" t="s">
-        <v>298</v>
-      </c>
       <c r="D50" s="5" t="s">
         <v>299</v>
       </c>
     </row>
     <row r="51" spans="2:4" x14ac:dyDescent="0.2">
-      <c r="B51" s="6" t="s">
-        <v>300</v>
-      </c>
       <c r="D51" s="6" t="s">
         <v>264</v>
       </c>
     </row>
     <row r="53" spans="2:4" x14ac:dyDescent="0.2">
-      <c r="B53" s="5" t="s">
-        <v>301</v>
-      </c>
       <c r="D53" s="5" t="s">
         <v>302</v>
       </c>
     </row>
     <row r="54" spans="2:4" x14ac:dyDescent="0.2">
-      <c r="B54" s="6" t="s">
-        <v>303</v>
-      </c>
       <c r="D54" s="6" t="s">
         <v>267</v>
       </c>
@@ -5151,29 +5127,15 @@
       <c r="B3" s="3" t="s">
         <v>135</v>
       </c>
-      <c r="D3" s="3" t="s">
-        <v>136</v>
-      </c>
     </row>
     <row r="4" spans="2:4" x14ac:dyDescent="0.2">
       <c r="B4" s="4" t="s">
         <v>137</v>
       </c>
-      <c r="D4" s="4" t="s">
-        <v>138</v>
-      </c>
     </row>
     <row r="5" spans="2:4" ht="16.5" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.25"/>
-    <row r="6" spans="2:4" ht="16.5" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="D6" s="3" t="s">
-        <v>139</v>
-      </c>
-    </row>
-    <row r="7" spans="2:4" ht="16.5" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="D7" s="4" t="s">
-        <v>140</v>
-      </c>
-    </row>
+    <row r="6" spans="2:4" ht="16.5" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.25"/>
+    <row r="7" spans="2:4" ht="16.5" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.25"/>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.51180555555555496" footer="0.51180555555555496"/>
   <pageSetup paperSize="0" scale="0" firstPageNumber="0" orientation="portrait" usePrinterDefaults="0" horizontalDpi="0" verticalDpi="0" copies="0"/>

--- a/DEV/org.openl.rules/test/rules/helpers/RulesUtilsTest.xlsx
+++ b/DEV/org.openl.rules/test/rules/helpers/RulesUtilsTest.xlsx
@@ -40,7 +40,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="748" uniqueCount="461">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="712" uniqueCount="461">
   <si>
     <t>Method Object copyObject(Object o)</t>
   </si>
@@ -5170,7 +5170,7 @@
 
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0900-000000000000}">
-  <dimension ref="A2:AMK126"/>
+  <dimension ref="A2:AMK72"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="9.5" customWidth="1" collapsed="1"/>
@@ -5482,186 +5482,6 @@
     <row r="72" spans="2:2" x14ac:dyDescent="0.2">
       <c r="B72" s="6" t="s">
         <v>190</v>
-      </c>
-    </row>
-    <row r="74" spans="2:2" x14ac:dyDescent="0.2">
-      <c r="B74" s="5" t="s">
-        <v>191</v>
-      </c>
-    </row>
-    <row r="75" spans="2:2" x14ac:dyDescent="0.2">
-      <c r="B75" s="6" t="s">
-        <v>192</v>
-      </c>
-    </row>
-    <row r="77" spans="2:2" x14ac:dyDescent="0.2">
-      <c r="B77" s="5" t="s">
-        <v>193</v>
-      </c>
-    </row>
-    <row r="78" spans="2:2" x14ac:dyDescent="0.2">
-      <c r="B78" s="6" t="s">
-        <v>192</v>
-      </c>
-    </row>
-    <row r="80" spans="2:2" x14ac:dyDescent="0.2">
-      <c r="B80" s="5" t="s">
-        <v>194</v>
-      </c>
-    </row>
-    <row r="81" spans="2:2" x14ac:dyDescent="0.2">
-      <c r="B81" s="6" t="s">
-        <v>192</v>
-      </c>
-    </row>
-    <row r="83" spans="2:2" x14ac:dyDescent="0.2">
-      <c r="B83" s="5" t="s">
-        <v>195</v>
-      </c>
-    </row>
-    <row r="84" spans="2:2" x14ac:dyDescent="0.2">
-      <c r="B84" s="6" t="s">
-        <v>192</v>
-      </c>
-    </row>
-    <row r="86" spans="2:2" x14ac:dyDescent="0.2">
-      <c r="B86" s="5" t="s">
-        <v>196</v>
-      </c>
-    </row>
-    <row r="87" spans="2:2" x14ac:dyDescent="0.2">
-      <c r="B87" s="6" t="s">
-        <v>197</v>
-      </c>
-    </row>
-    <row r="89" spans="2:2" x14ac:dyDescent="0.2">
-      <c r="B89" s="5" t="s">
-        <v>198</v>
-      </c>
-    </row>
-    <row r="90" spans="2:2" x14ac:dyDescent="0.2">
-      <c r="B90" s="6" t="s">
-        <v>199</v>
-      </c>
-    </row>
-    <row r="92" spans="2:2" x14ac:dyDescent="0.2">
-      <c r="B92" s="5" t="s">
-        <v>200</v>
-      </c>
-    </row>
-    <row r="93" spans="2:2" x14ac:dyDescent="0.2">
-      <c r="B93" s="6" t="s">
-        <v>201</v>
-      </c>
-    </row>
-    <row r="95" spans="2:2" x14ac:dyDescent="0.2">
-      <c r="B95" s="5" t="s">
-        <v>202</v>
-      </c>
-    </row>
-    <row r="96" spans="2:2" x14ac:dyDescent="0.2">
-      <c r="B96" s="6" t="s">
-        <v>203</v>
-      </c>
-    </row>
-    <row r="98" spans="2:2" x14ac:dyDescent="0.2">
-      <c r="B98" s="5" t="s">
-        <v>204</v>
-      </c>
-    </row>
-    <row r="99" spans="2:2" x14ac:dyDescent="0.2">
-      <c r="B99" s="6" t="s">
-        <v>205</v>
-      </c>
-    </row>
-    <row r="101" spans="2:2" x14ac:dyDescent="0.2">
-      <c r="B101" s="5" t="s">
-        <v>206</v>
-      </c>
-    </row>
-    <row r="102" spans="2:2" x14ac:dyDescent="0.2">
-      <c r="B102" s="6" t="s">
-        <v>207</v>
-      </c>
-    </row>
-    <row r="104" spans="2:2" x14ac:dyDescent="0.2">
-      <c r="B104" s="5" t="s">
-        <v>208</v>
-      </c>
-    </row>
-    <row r="105" spans="2:2" x14ac:dyDescent="0.2">
-      <c r="B105" s="6" t="s">
-        <v>209</v>
-      </c>
-    </row>
-    <row r="107" spans="2:2" x14ac:dyDescent="0.2">
-      <c r="B107" s="5" t="s">
-        <v>210</v>
-      </c>
-    </row>
-    <row r="108" spans="2:2" x14ac:dyDescent="0.2">
-      <c r="B108" s="6" t="s">
-        <v>209</v>
-      </c>
-    </row>
-    <row r="110" spans="2:2" x14ac:dyDescent="0.2">
-      <c r="B110" s="5" t="s">
-        <v>211</v>
-      </c>
-    </row>
-    <row r="111" spans="2:2" x14ac:dyDescent="0.2">
-      <c r="B111" s="6" t="s">
-        <v>212</v>
-      </c>
-    </row>
-    <row r="113" spans="2:2" x14ac:dyDescent="0.2">
-      <c r="B113" s="5" t="s">
-        <v>213</v>
-      </c>
-    </row>
-    <row r="114" spans="2:2" x14ac:dyDescent="0.2">
-      <c r="B114" s="6" t="s">
-        <v>214</v>
-      </c>
-    </row>
-    <row r="116" spans="2:2" x14ac:dyDescent="0.2">
-      <c r="B116" s="5" t="s">
-        <v>215</v>
-      </c>
-    </row>
-    <row r="117" spans="2:2" x14ac:dyDescent="0.2">
-      <c r="B117" s="6" t="s">
-        <v>216</v>
-      </c>
-    </row>
-    <row r="119" spans="2:2" x14ac:dyDescent="0.2">
-      <c r="B119" s="5" t="s">
-        <v>217</v>
-      </c>
-    </row>
-    <row r="120" spans="2:2" x14ac:dyDescent="0.2">
-      <c r="B120" s="6" t="s">
-        <v>218</v>
-      </c>
-    </row>
-    <row r="122" spans="2:2" x14ac:dyDescent="0.2">
-      <c r="B122" s="5" t="s">
-        <v>219</v>
-      </c>
-    </row>
-    <row r="123" spans="2:2" x14ac:dyDescent="0.2">
-      <c r="B123" s="6" t="s">
-        <v>220</v>
-      </c>
-    </row>
-    <row r="125" spans="2:2" x14ac:dyDescent="0.2">
-      <c r="B125" s="5" t="s">
-        <v>221</v>
-      </c>
-    </row>
-    <row r="126" spans="2:2" x14ac:dyDescent="0.2">
-      <c r="B126" s="6" t="s">
-        <v>220</v>
       </c>
     </row>
   </sheetData>
